--- a/data/satisfaction_summary/2026/Q3/Q3客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/Q3/Q3客户类型满意度汇总表.xlsx
@@ -613,22 +613,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>9.686511627906976</v>
+        <v>9.76</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>9.758584070796459</v>
+        <v>9.77</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.546046511627907</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>9.682191780821919</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>9.038</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.681162790697673</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9.905663716814159</v>
+        <v>9.91</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9.464186046511628</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9.713013698630137</v>
+        <v>9.73</v>
       </c>
       <c r="G4" s="4" t="n">
         <v>9.42</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>9.136857142857144</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -665,20 +665,20 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.771627906976743</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>9.615813953488372</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9.690000000000001</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>9.191428571428572</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -689,22 +689,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.857906976744186</v>
+        <v>9.85</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>9.917168141592921</v>
+        <v>9.92</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.826744186046513</v>
+        <v>9.83</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9.785205479452054</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>9.725</v>
+        <v>9.84</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>9.379714285714286</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
@@ -715,20 +715,20 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.778372093023256</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9.923185840707966</v>
+        <v>9.92</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.66860465116279</v>
+        <v>9.67</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.747397260273974</v>
+        <v>9.75</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>9.018857142857142</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -745,10 +745,10 @@
         <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.605</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.882666666666667</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.527209302325581</v>
+        <v>9.51</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.168372093023256</v>
+        <v>9.17</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>9.729714285714286</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.610697674418605</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.472790697674418</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>10</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>9.471428571428572</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>9.395172413793103</v>
+        <v>9.4</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.966551724137933</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
@@ -866,7 +866,7 @@
       </c>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>9.810416666666669</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.746511627906976</v>
+        <v>9.32</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.964601769911503</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9.977209302325582</v>
+        <v>9.98</v>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>9.903023255813954</v>
+        <v>9.92</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>9.764418604651164</v>
+        <v>9.76</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
@@ -1037,13 +1037,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9.779069767441861</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>9.744424778761061</v>
+        <v>9.77</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.638372093023255</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>9.927142857142856</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>9.464999999999998</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
@@ -1089,16 +1089,16 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>9.945</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.855</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9.981333333333335</v>
+        <v>9.98</v>
       </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n">
@@ -1113,13 +1113,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.944482758620689</v>
+        <v>9.94</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>9.934285714285714</v>
+        <v>9.93</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.898620689655171</v>
+        <v>9.9</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>10</v>
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.659302325581395</v>
+        <v>9.66</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.494186046511627</v>
+        <v>9.49</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n">
-        <v>9.817428571428572</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
@@ -1165,28 +1165,28 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="4" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>9.92</v>
+        <v>9.93</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.609999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>9.68</v>
+        <v>9.56</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9.52</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>累计总分按独立周期等权平均；指标和客户类型按周期实际贡献加权，详见周期计算与权重核对。</t>
+          <t>客群总分为分表有效一级指标的等权均值，总表各项与分表一致；表底各项为有效客群对应值的等权均值，均保留两位小数。各期均值与原累计权重另列参考。</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1368,31 +1368,58 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>各期均值</t>
+          <t>客群等权汇总</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>各期均值（参考）</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
         <v>9.74</v>
       </c>
-      <c r="C5" s="10" t="n">
+      <c r="C6" s="10" t="n">
         <v>9.92</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D6" s="10" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E6" s="10" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F6" s="10" t="n">
         <v>9.68</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G6" s="10" t="n">
         <v>9.52</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I6" s="10" t="n">
         <v>9.74</v>
       </c>
     </row>
@@ -1441,12 +1468,12 @@
       </c>
       <c r="E1" s="8" t="inlineStr">
         <is>
-          <t>累计权重</t>
+          <t>原累计参考权重</t>
         </is>
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
-          <t>贡献</t>
+          <t>原累计参考贡献</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6350,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>核对项</t>
+          <t>原累计口径核对项（非总表取数依据）</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
